--- a/underwriting/sample/Riverbend Apartments - T12.xlsx
+++ b/underwriting/sample/Riverbend Apartments - T12.xlsx
@@ -461,7 +461,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Book = Accrual   (fictional sample data - Cedar Ridge Capital demo)</t>
+          <t>Book = Accrual   (fictional sample data - Demo Portfolio Capital demo)</t>
         </is>
       </c>
     </row>
